--- a/data/trans_orig/IP1012-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP1012-Clase-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4231</t>
+          <t>2970</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>100121</t>
+          <t>101382</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93496</t>
+          <t>94164</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>197278</t>
+          <t>197371</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3250</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3416</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>82720</t>
+          <t>82713</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>170147</t>
+          <t>169943</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4300</t>
+          <t>5903</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>4331</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>95032</t>
+          <t>93429</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>162394</t>
+          <t>162393</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4147</t>
+          <t>4653</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>4882</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>197927</t>
+          <t>197421</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>398033</t>
+          <t>397925</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3232</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>100888</t>
+          <t>100882</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>227877</t>
+          <t>227977</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3694</t>
+          <t>3727</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>640</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5928</t>
+          <t>5952</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>736</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7315</t>
+          <t>6602</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>71176</t>
+          <t>71143</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>66464</t>
+          <t>66440</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>71750</t>
+          <t>71752</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>139947</t>
+          <t>140660</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>146606</t>
+          <t>146526</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>633</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6236</t>
+          <t>5725</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t>2798</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>11538</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4220</t>
+          <t>4073</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13982</t>
+          <t>13333</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>632620</t>
+          <t>633131</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>638222</t>
+          <t>638223</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>673272</t>
+          <t>673065</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>681952</t>
+          <t>681805</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1309477</t>
+          <t>1310126</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1319239</t>
+          <t>1319386</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4252</t>
+          <t>4115</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3089</t>
+          <t>3391</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>84187</t>
+          <t>84324</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>175114</t>
+          <t>174812</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>3902</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3132</t>
+          <t>3125</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>92566</t>
+          <t>92209</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>185708</t>
+          <t>185715</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2547</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>3086</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>84343</t>
+          <t>83453</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>167998</t>
+          <t>168009</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>6485</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>631</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6944</t>
+          <t>6385</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>202970</t>
+          <t>201924</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>221641</t>
+          <t>220379</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>425548</t>
+          <t>426107</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>431856</t>
+          <t>431861</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3717</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>651</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>918</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7521</t>
+          <t>7936</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>145452</t>
+          <t>144210</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>132928</t>
+          <t>133005</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>139180</t>
+          <t>139183</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>281482</t>
+          <t>281067</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>287986</t>
+          <t>288085</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,68%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>655</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6095</t>
+          <t>7193</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2284</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10486</t>
+          <t>10648</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3660</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13759</t>
+          <t>13879</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>667986</t>
+          <t>666888</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>673424</t>
+          <t>673426</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>703015</t>
+          <t>702853</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>711171</t>
+          <t>711217</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1373823</t>
+          <t>1373703</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1383922</t>
+          <t>1383904</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4828</t>
+          <t>4163</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4195</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -6150,7 +6150,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>94969</t>
+          <t>95634</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>178692</t>
+          <t>178211</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3830</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -6493,7 +6493,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>109671</t>
+          <t>108961</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>214630</t>
+          <t>213933</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3051</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3079</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -7179,7 +7179,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>207803</t>
+          <t>207530</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>431352</t>
+          <t>431325</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>756</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7473</t>
+          <t>6431</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>714</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6262</t>
+          <t>6813</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>702264</t>
+          <t>703306</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>709086</t>
+          <t>708981</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1374977</t>
+          <t>1374426</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1380592</t>
+          <t>1380525</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">

--- a/data/trans_orig/IP1012-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP1012-Clase-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -727,102 +727,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4039</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,14%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>634</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2970</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3833</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,61%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>3,67%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1307</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3381</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4125</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1307</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4527</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>96872</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>93506</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,31%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>95,86%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>103718</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>101382</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>100519</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>104352</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,39%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>97,15%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>96,33%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>96872</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>94164</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,31%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>96,53%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>297</t>
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>197371</t>
+          <t>197773</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,107 +1065,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3809</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>644</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3257</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3241</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>3,79%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3416</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>85326</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>82161</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,25%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>95,57%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>87389</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>85326</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>82713</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>169943</t>
+          <t>170118</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1296,52 +1296,52 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
           <t>87389</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>87389</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>87389</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,107 +1408,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>866</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4332</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,36%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>866</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5903</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>5172</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>5,94%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>866</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4331</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>98466</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>95000</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,13%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,64%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>67392</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>98466</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>93429</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,13%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>162393</t>
+          <t>161552</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,107 +1751,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1349</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5278</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1349</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4653</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4592</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1349</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4882</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>200725</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>196796</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,33%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,39%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>303</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>200733</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>200725</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>197421</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,33%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>397925</t>
+          <t>398215</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>303</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,107 +2094,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3238</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,62%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,11%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>3,08%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3194</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3433</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -2207,74 +2207,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>103478</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>100882</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>100915</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>104120</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,38%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96,89%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>96,92%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>347</t>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>227977</t>
+          <t>228216</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2437,72 +2437,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2157</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>6220</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2,98%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>8,59%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>733</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3727</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4344</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,98%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>4,98%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>2157</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>640</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5952</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>732</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6602</t>
+          <t>7444</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -2550,74 +2550,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>70235</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>66172</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>71751</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>97,02%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>91,41%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>99,12%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>74137</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>71143</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>70526</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>99,02%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>95,02%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>94,2%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>70235</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>66440</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>71752</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>97,02%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>91,78%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>99,12%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>215</t>
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>140660</t>
+          <t>139818</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>146526</t>
+          <t>146530</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2780,72 +2780,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>5689</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2611</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>10809</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>2009</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>5725</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5606</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,31%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,1%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>5689</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>2798</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>11538</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4073</t>
+          <t>4008</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13333</t>
+          <t>12992</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -2893,74 +2893,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1021</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>678914</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>673794</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>681992</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,17%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>98,42%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,62%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>950</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>636847</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>633131</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>638223</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>633250</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>638224</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,69%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>99,12%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>99,9%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1021</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>678914</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>673065</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>681805</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,17%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>98,31%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,59%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>1971</t>
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1310126</t>
+          <t>1310467</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1319386</t>
+          <t>1319451</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1029</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>953</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1029</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3189,7 +3189,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3357,107 +3357,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>746</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4115</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3756</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,84%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,65%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>4,25%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>746</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3723</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>746</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3391</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -3470,74 +3470,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>87693</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>84324</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>84683</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>88439</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,16%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,35%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,75%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>257</t>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>174812</t>
+          <t>174480</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3583,57 +3583,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3700,107 +3700,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3155</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,28%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>624</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3902</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3656</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3125</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -3813,72 +3813,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>95487</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>92956</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,35%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,72%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>92729</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>95487</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>92209</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,35%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>185715</t>
+          <t>185184</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3926,57 +3926,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4043,107 +4043,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3132</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>619</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3437</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3127</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,96%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3086</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -4156,72 +4156,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>86271</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>83758</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,29%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,4%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>84205</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>86271</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>83453</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,29%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>168009</t>
+          <t>167968</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4269,57 +4269,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4386,72 +4386,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1658</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6295</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,77%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3704</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3484</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1658</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6485</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>632</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6385</t>
+          <t>6724</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -4499,74 +4499,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>225206</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>220569</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,27%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,23%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>297</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>204972</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>201924</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>202144</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>205628</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,68%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,2%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,31%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>225206</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>220379</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,27%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,14%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>617</t>
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>426107</t>
+          <t>425768</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>431861</t>
+          <t>431860</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4612,57 +4612,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>298</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4729,72 +4729,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2364</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6972</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,99%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>915</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4959</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4300</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,61%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,32%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2364</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>651</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6829</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>915</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7936</t>
+          <t>8597</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -4842,74 +4842,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>137470</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>132862</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>139182</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,31%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,01%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,53%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>148254</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>144210</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>144869</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>149169</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,39%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96,68%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>97,12%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>137470</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>133005</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>139183</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,31%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>95,12%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,53%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>404</t>
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>281067</t>
+          <t>280406</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>288085</t>
+          <t>288088</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4955,57 +4955,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5185,47 +5185,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>53911</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -5298,57 +5298,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>5266</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>10398</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>2318</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>655</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>7193</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>6322</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,1%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>5266</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>2284</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>10648</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3678</t>
+          <t>3748</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13879</t>
+          <t>13424</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -5528,74 +5528,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1011</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>708235</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>703103</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>711478</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,26%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>98,54%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,72%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>970</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>671763</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>666888</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>673426</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>667759</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>673425</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,66%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>98,93%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>99,06%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>99,9%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1011</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>708235</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>702853</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>711217</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,26%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>98,51%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,68%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>1981</t>
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1373703</t>
+          <t>1374158</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1383904</t>
+          <t>1383834</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -5641,57 +5641,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1018</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>973</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1018</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5813,7 +5813,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5824,7 +5824,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5992,107 +5992,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1359</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4673</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1359</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4163</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4865</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1359</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4676</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -6105,72 +6105,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>98438</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>95124</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,64%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>95,32%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>98438</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>95634</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,64%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>178211</t>
+          <t>178022</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6218,57 +6218,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6335,107 +6335,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3830</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>759</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3785</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4135</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>759</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4527</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -6448,72 +6448,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>111987</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>108916</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,33%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,6%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>105714</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>111987</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>108961</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,33%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>213933</t>
+          <t>214325</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6561,57 +6561,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6791,47 +6791,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>61840</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -6904,57 +6904,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7021,107 +7021,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3121</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>618</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3324</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3563</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>618</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3106</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -7134,72 +7134,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>210236</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>207733</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,71%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,52%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>210236</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>207530</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>431325</t>
+          <t>430868</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7247,57 +7247,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7477,47 +7477,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>136194</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -7590,57 +7590,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7820,47 +7820,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>61087</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -7933,57 +7933,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8050,92 +8050,92 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2736</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>6898</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>2736</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>756</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>6431</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>2736</t>
-        </is>
-      </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>712</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6813</t>
+          <t>6832</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8168,67 +8168,67 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>707001</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>702839</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>709024</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,61%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>99,03%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,9%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>1013</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
           <t>671502</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1013</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>707001</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>703306</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>708981</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,61%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1374426</t>
+          <t>1374407</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1380525</t>
+          <t>1380527</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8276,57 +8276,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>1013</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1017</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
